--- a/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="627">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>
@@ -1391,6 +1391,21 @@
     <t xml:space="preserve">うつろわざる</t>
   </si>
   <si>
+    <t xml:space="preserve">114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふわふわの</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.253</t>
   </si>
   <si>
@@ -1436,6 +1451,9 @@
     <t xml:space="preserve">EA 23.245</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.283</t>
+  </si>
+  <si>
     <t xml:space="preserve">暗物质</t>
   </si>
   <si>
@@ -1715,6 +1733,9 @@
     <t xml:space="preserve">不朽铁</t>
   </si>
   <si>
+    <t xml:space="preserve">云</t>
+  </si>
+  <si>
     <t xml:space="preserve">虚无的</t>
   </si>
   <si>
@@ -1872,6 +1893,9 @@
   </si>
   <si>
     <t xml:space="preserve">无限的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">软绵绵的</t>
   </si>
 </sst>
 </file>
@@ -1977,10 +2001,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C3" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1989,7 +2013,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -2003,10 +2027,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C4" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -2015,7 +2039,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -2029,10 +2053,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C5" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -2041,7 +2065,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -2055,10 +2079,10 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C6" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -2067,7 +2091,7 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
@@ -2081,7 +2105,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -2100,7 +2124,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
@@ -2112,7 +2136,7 @@
         <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="G8" t="s">
         <v>35</v>
@@ -2126,10 +2150,10 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C9" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D9" t="s">
         <v>38</v>
@@ -2145,10 +2169,10 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C10" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D10" t="s">
         <v>41</v>
@@ -2164,10 +2188,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C11" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>
@@ -2176,7 +2200,7 @@
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="G11" t="s">
         <v>46</v>
@@ -2190,10 +2214,10 @@
         <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C12" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2202,7 +2226,7 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="G12" t="s">
         <v>51</v>
@@ -2216,10 +2240,10 @@
         <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C13" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2228,7 +2252,7 @@
         <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="G13" t="s">
         <v>56</v>
@@ -2242,10 +2266,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C14" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D14" t="s">
         <v>59</v>
@@ -2261,7 +2285,7 @@
         <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C15" t="s">
         <v>63</v>
@@ -2273,7 +2297,7 @@
         <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="G15" t="s">
         <v>64</v>
@@ -2287,10 +2311,10 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C16" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D16" t="s">
         <v>67</v>
@@ -2299,7 +2323,7 @@
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="G16" t="s">
         <v>69</v>
@@ -2313,10 +2337,10 @@
         <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C17" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D17" t="s">
         <v>72</v>
@@ -2325,7 +2349,7 @@
         <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
@@ -2339,10 +2363,10 @@
         <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C18" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D18" t="s">
         <v>77</v>
@@ -2351,7 +2375,7 @@
         <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="G18" t="s">
         <v>79</v>
@@ -2365,10 +2389,10 @@
         <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C19" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D19" t="s">
         <v>82</v>
@@ -2377,7 +2401,7 @@
         <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="G19" t="s">
         <v>84</v>
@@ -2391,10 +2415,10 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C20" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D20" t="s">
         <v>87</v>
@@ -2403,7 +2427,7 @@
         <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="G20" t="s">
         <v>89</v>
@@ -2417,10 +2441,10 @@
         <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C21" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D21" t="s">
         <v>92</v>
@@ -2429,7 +2453,7 @@
         <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="G21" t="s">
         <v>94</v>
@@ -2443,10 +2467,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C22" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -2455,7 +2479,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -2469,10 +2493,10 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C23" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D23" t="s">
         <v>102</v>
@@ -2481,7 +2505,7 @@
         <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="G23" t="s">
         <v>104</v>
@@ -2495,7 +2519,7 @@
         <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C24" t="s">
         <v>108</v>
@@ -2507,7 +2531,7 @@
         <v>108</v>
       </c>
       <c r="F24" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="G24" t="s">
         <v>109</v>
@@ -2521,10 +2545,10 @@
         <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C25" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D25" t="s">
         <v>112</v>
@@ -2533,7 +2557,7 @@
         <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="G25" t="s">
         <v>114</v>
@@ -2547,7 +2571,7 @@
         <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C26" t="s">
         <v>118</v>
@@ -2559,7 +2583,7 @@
         <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="G26" t="s">
         <v>119</v>
@@ -2573,7 +2597,7 @@
         <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C27" t="s">
         <v>123</v>
@@ -2585,7 +2609,7 @@
         <v>123</v>
       </c>
       <c r="F27" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="G27" t="s">
         <v>124</v>
@@ -2599,10 +2623,10 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C28" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D28" t="s">
         <v>127</v>
@@ -2611,7 +2635,7 @@
         <v>128</v>
       </c>
       <c r="F28" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="G28" t="s">
         <v>129</v>
@@ -2625,10 +2649,10 @@
         <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C29" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D29" t="s">
         <v>132</v>
@@ -2637,7 +2661,7 @@
         <v>133</v>
       </c>
       <c r="F29" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="G29" t="s">
         <v>134</v>
@@ -2651,10 +2675,10 @@
         <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C30" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D30" t="s">
         <v>137</v>
@@ -2663,7 +2687,7 @@
         <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="G30" t="s">
         <v>139</v>
@@ -2677,10 +2701,10 @@
         <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C31" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
@@ -2696,10 +2720,10 @@
         <v>144</v>
       </c>
       <c r="B32" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C32" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -2708,7 +2732,7 @@
         <v>146</v>
       </c>
       <c r="F32" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G32" t="s">
         <v>147</v>
@@ -2722,10 +2746,10 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C33" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D33" t="s">
         <v>150</v>
@@ -2741,10 +2765,10 @@
         <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C34" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D34" t="s">
         <v>153</v>
@@ -2760,10 +2784,10 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -2779,10 +2803,10 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C36" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
@@ -2798,7 +2822,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C37" t="s">
         <v>163</v>
@@ -2817,10 +2841,10 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C38" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D38" t="s">
         <v>165</v>
@@ -2836,10 +2860,10 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C39" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D39" t="s">
         <v>168</v>
@@ -2855,10 +2879,10 @@
         <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C40" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D40" t="s">
         <v>171</v>
@@ -2874,10 +2898,10 @@
         <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C41" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D41" t="s">
         <v>174</v>
@@ -2893,7 +2917,7 @@
         <v>176</v>
       </c>
       <c r="B42" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C42" t="s">
         <v>178</v>
@@ -2905,7 +2929,7 @@
         <v>178</v>
       </c>
       <c r="F42" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="G42" t="s">
         <v>179</v>
@@ -2919,7 +2943,7 @@
         <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C43" t="s">
         <v>183</v>
@@ -2931,7 +2955,7 @@
         <v>183</v>
       </c>
       <c r="F43" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="G43" t="s">
         <v>184</v>
@@ -2945,10 +2969,10 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C44" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D44" t="s">
         <v>187</v>
@@ -2964,10 +2988,10 @@
         <v>189</v>
       </c>
       <c r="B45" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C45" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D45" t="s">
         <v>190</v>
@@ -2976,7 +3000,7 @@
         <v>191</v>
       </c>
       <c r="F45" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="G45" t="s">
         <v>192</v>
@@ -2990,10 +3014,10 @@
         <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C46" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D46" t="s">
         <v>195</v>
@@ -3002,7 +3026,7 @@
         <v>196</v>
       </c>
       <c r="F46" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="G46" t="s">
         <v>197</v>
@@ -3016,10 +3040,10 @@
         <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C47" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D47" t="s">
         <v>200</v>
@@ -3035,7 +3059,7 @@
         <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C48" t="s">
         <v>204</v>
@@ -3054,10 +3078,10 @@
         <v>205</v>
       </c>
       <c r="B49" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C49" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D49" t="s">
         <v>206</v>
@@ -3073,10 +3097,10 @@
         <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C50" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D50" t="s">
         <v>209</v>
@@ -3092,7 +3116,7 @@
         <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C51" t="s">
         <v>213</v>
@@ -3111,10 +3135,10 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C52" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D52" t="s">
         <v>215</v>
@@ -3130,7 +3154,7 @@
         <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C53" t="s">
         <v>219</v>
@@ -3149,10 +3173,10 @@
         <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C54" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D54" t="s">
         <v>221</v>
@@ -3168,10 +3192,10 @@
         <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C55" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D55" t="s">
         <v>224</v>
@@ -3187,10 +3211,10 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C56" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D56" t="s">
         <v>227</v>
@@ -3206,10 +3230,10 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C57" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D57" t="s">
         <v>230</v>
@@ -3225,10 +3249,10 @@
         <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C58" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
@@ -3237,7 +3261,7 @@
         <v>234</v>
       </c>
       <c r="F58" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="G58" t="s">
         <v>235</v>
@@ -3251,10 +3275,10 @@
         <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C59" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D59" t="s">
         <v>238</v>
@@ -3270,7 +3294,7 @@
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C60" t="s">
         <v>242</v>
@@ -3289,10 +3313,10 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C61" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D61" t="s">
         <v>244</v>
@@ -3308,10 +3332,10 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C62" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D62" t="s">
         <v>247</v>
@@ -3327,10 +3351,10 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C63" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D63" t="s">
         <v>250</v>
@@ -3346,10 +3370,10 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C64" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D64" t="s">
         <v>253</v>
@@ -3365,10 +3389,10 @@
         <v>255</v>
       </c>
       <c r="B65" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C65" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D65" t="s">
         <v>256</v>
@@ -3377,7 +3401,7 @@
         <v>257</v>
       </c>
       <c r="F65" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="G65" t="s">
         <v>258</v>
@@ -3391,10 +3415,10 @@
         <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C66" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D66" t="s">
         <v>261</v>
@@ -3410,10 +3434,10 @@
         <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C67" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D67" t="s">
         <v>264</v>
@@ -3429,10 +3453,10 @@
         <v>266</v>
       </c>
       <c r="B68" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C68" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D68" t="s">
         <v>267</v>
@@ -3448,7 +3472,7 @@
         <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C69" t="s">
         <v>271</v>
@@ -3467,7 +3491,7 @@
         <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C70" t="s">
         <v>274</v>
@@ -3486,10 +3510,10 @@
         <v>275</v>
       </c>
       <c r="B71" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C71" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D71" t="s">
         <v>276</v>
@@ -3498,7 +3522,7 @@
         <v>277</v>
       </c>
       <c r="F71" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="G71" t="s">
         <v>278</v>
@@ -3512,10 +3536,10 @@
         <v>280</v>
       </c>
       <c r="B72" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C72" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D72" t="s">
         <v>281</v>
@@ -3524,7 +3548,7 @@
         <v>282</v>
       </c>
       <c r="F72" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="G72" t="s">
         <v>283</v>
@@ -3538,10 +3562,10 @@
         <v>285</v>
       </c>
       <c r="B73" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C73" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D73" t="s">
         <v>286</v>
@@ -3550,7 +3574,7 @@
         <v>287</v>
       </c>
       <c r="F73" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="G73" t="s">
         <v>288</v>
@@ -3564,10 +3588,10 @@
         <v>290</v>
       </c>
       <c r="B74" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C74" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D74" t="s">
         <v>291</v>
@@ -3576,7 +3600,7 @@
         <v>292</v>
       </c>
       <c r="F74" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="G74" t="s">
         <v>293</v>
@@ -3590,10 +3614,10 @@
         <v>295</v>
       </c>
       <c r="B75" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C75" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D75" t="s">
         <v>296</v>
@@ -3602,7 +3626,7 @@
         <v>297</v>
       </c>
       <c r="F75" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="G75" t="s">
         <v>298</v>
@@ -3616,10 +3640,10 @@
         <v>300</v>
       </c>
       <c r="B76" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C76" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D76" t="s">
         <v>301</v>
@@ -3628,7 +3652,7 @@
         <v>302</v>
       </c>
       <c r="F76" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="G76" t="s">
         <v>303</v>
@@ -3642,10 +3666,10 @@
         <v>305</v>
       </c>
       <c r="B77" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C77" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D77" t="s">
         <v>306</v>
@@ -3654,7 +3678,7 @@
         <v>307</v>
       </c>
       <c r="F77" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G77" t="s">
         <v>308</v>
@@ -3668,10 +3692,10 @@
         <v>310</v>
       </c>
       <c r="B78" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C78" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D78" t="s">
         <v>311</v>
@@ -3680,7 +3704,7 @@
         <v>312</v>
       </c>
       <c r="F78" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="G78" t="s">
         <v>313</v>
@@ -3694,10 +3718,10 @@
         <v>315</v>
       </c>
       <c r="B79" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C79" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D79" t="s">
         <v>316</v>
@@ -3706,7 +3730,7 @@
         <v>317</v>
       </c>
       <c r="F79" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="G79" t="s">
         <v>318</v>
@@ -3720,10 +3744,10 @@
         <v>320</v>
       </c>
       <c r="B80" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C80" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D80" t="s">
         <v>321</v>
@@ -3732,7 +3756,7 @@
         <v>322</v>
       </c>
       <c r="F80" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="G80" t="s">
         <v>323</v>
@@ -3746,10 +3770,10 @@
         <v>325</v>
       </c>
       <c r="B81" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C81" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D81" t="s">
         <v>326</v>
@@ -3758,7 +3782,7 @@
         <v>327</v>
       </c>
       <c r="F81" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="G81" t="s">
         <v>328</v>
@@ -3772,10 +3796,10 @@
         <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C82" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D82" t="s">
         <v>331</v>
@@ -3791,10 +3815,10 @@
         <v>333</v>
       </c>
       <c r="B83" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C83" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D83" t="s">
         <v>334</v>
@@ -3803,7 +3827,7 @@
         <v>335</v>
       </c>
       <c r="F83" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="G83" t="s">
         <v>336</v>
@@ -3817,10 +3841,10 @@
         <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C84" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D84" t="s">
         <v>339</v>
@@ -3829,7 +3853,7 @@
         <v>340</v>
       </c>
       <c r="F84" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="G84" t="s">
         <v>341</v>
@@ -3843,7 +3867,7 @@
         <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C85" t="s">
         <v>345</v>
@@ -3862,10 +3886,10 @@
         <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C86" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D86" t="s">
         <v>347</v>
@@ -3881,10 +3905,10 @@
         <v>349</v>
       </c>
       <c r="B87" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C87" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D87" t="s">
         <v>350</v>
@@ -3900,10 +3924,10 @@
         <v>352</v>
       </c>
       <c r="B88" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C88" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D88" t="s">
         <v>353</v>
@@ -3919,10 +3943,10 @@
         <v>355</v>
       </c>
       <c r="B89" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C89" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D89" t="s">
         <v>356</v>
@@ -3938,10 +3962,10 @@
         <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C90" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D90" t="s">
         <v>359</v>
@@ -3957,7 +3981,7 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C91" t="s">
         <v>363</v>
@@ -3976,10 +4000,10 @@
         <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C92" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D92" t="s">
         <v>365</v>
@@ -3995,10 +4019,10 @@
         <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C93" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D93" t="s">
         <v>368</v>
@@ -4014,10 +4038,10 @@
         <v>370</v>
       </c>
       <c r="B94" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C94" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D94" t="s">
         <v>371</v>
@@ -4026,7 +4050,7 @@
         <v>372</v>
       </c>
       <c r="F94" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="G94" t="s">
         <v>373</v>
@@ -4040,10 +4064,10 @@
         <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C95" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="D95" t="s">
         <v>376</v>
@@ -4059,10 +4083,10 @@
         <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C96" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D96" t="s">
         <v>379</v>
@@ -4078,10 +4102,10 @@
         <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C97" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D97" t="s">
         <v>382</v>
@@ -4097,7 +4121,7 @@
         <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C98" t="s">
         <v>386</v>
@@ -4116,10 +4140,10 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C99" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D99" t="s">
         <v>388</v>
@@ -4135,10 +4159,10 @@
         <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C100" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D100" t="s">
         <v>391</v>
@@ -4154,7 +4178,7 @@
         <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C101" t="s">
         <v>395</v>
@@ -4173,10 +4197,10 @@
         <v>396</v>
       </c>
       <c r="B102" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C102" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D102" t="s">
         <v>397</v>
@@ -4185,7 +4209,7 @@
         <v>398</v>
       </c>
       <c r="F102" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="G102" t="s">
         <v>399</v>
@@ -4199,10 +4223,10 @@
         <v>401</v>
       </c>
       <c r="B103" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C103" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D103" t="s">
         <v>402</v>
@@ -4218,10 +4242,10 @@
         <v>404</v>
       </c>
       <c r="B104" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C104" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="D104" t="s">
         <v>405</v>
@@ -4237,10 +4261,10 @@
         <v>407</v>
       </c>
       <c r="B105" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C105" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D105" t="s">
         <v>408</v>
@@ -4249,7 +4273,7 @@
         <v>409</v>
       </c>
       <c r="F105" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="G105" t="s">
         <v>410</v>
@@ -4263,10 +4287,10 @@
         <v>412</v>
       </c>
       <c r="B106" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C106" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="D106" t="s">
         <v>413</v>
@@ -4282,7 +4306,7 @@
         <v>415</v>
       </c>
       <c r="B107" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C107" t="s">
         <v>417</v>
@@ -4301,10 +4325,10 @@
         <v>418</v>
       </c>
       <c r="B108" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C108" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D108" t="s">
         <v>419</v>
@@ -4320,7 +4344,7 @@
         <v>421</v>
       </c>
       <c r="B109" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C109" t="s">
         <v>423</v>
@@ -4339,10 +4363,10 @@
         <v>424</v>
       </c>
       <c r="B110" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C110" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="D110" t="s">
         <v>425</v>
@@ -4351,7 +4375,7 @@
         <v>426</v>
       </c>
       <c r="F110" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="G110" t="s">
         <v>427</v>
@@ -4365,10 +4389,10 @@
         <v>429</v>
       </c>
       <c r="B111" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C111" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D111" t="s">
         <v>430</v>
@@ -4377,7 +4401,7 @@
         <v>431</v>
       </c>
       <c r="F111" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="G111" t="s">
         <v>318</v>
@@ -4391,10 +4415,10 @@
         <v>433</v>
       </c>
       <c r="B112" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C112" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D112" t="s">
         <v>434</v>
@@ -4403,7 +4427,7 @@
         <v>435</v>
       </c>
       <c r="F112" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="G112" t="s">
         <v>436</v>
@@ -4417,10 +4441,10 @@
         <v>438</v>
       </c>
       <c r="B113" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C113" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="D113" t="s">
         <v>439</v>
@@ -4429,7 +4453,7 @@
         <v>440</v>
       </c>
       <c r="F113" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="G113" t="s">
         <v>441</v>
@@ -4443,10 +4467,10 @@
         <v>443</v>
       </c>
       <c r="B114" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C114" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="D114" t="s">
         <v>444</v>
@@ -4455,7 +4479,7 @@
         <v>445</v>
       </c>
       <c r="F114" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="G114" t="s">
         <v>446</v>
@@ -4469,10 +4493,10 @@
         <v>448</v>
       </c>
       <c r="B115" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C115" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D115" t="s">
         <v>449</v>
@@ -4481,7 +4505,7 @@
         <v>450</v>
       </c>
       <c r="F115" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="G115" t="s">
         <v>451</v>
@@ -4495,10 +4519,10 @@
         <v>453</v>
       </c>
       <c r="B116" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C116" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D116" t="s">
         <v>454</v>
@@ -4507,13 +4531,39 @@
         <v>455</v>
       </c>
       <c r="F116" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="G116" t="s">
         <v>456</v>
       </c>
       <c r="H116" t="s">
         <v>457</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>458</v>
+      </c>
+      <c r="B117" t="s">
+        <v>478</v>
+      </c>
+      <c r="C117" t="s">
+        <v>572</v>
+      </c>
+      <c r="D117" t="s">
+        <v>459</v>
+      </c>
+      <c r="E117" t="s">
+        <v>460</v>
+      </c>
+      <c r="F117" t="s">
+        <v>626</v>
+      </c>
+      <c r="G117" t="s">
+        <v>461</v>
+      </c>
+      <c r="H117" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>
